--- a/src/Tests/Samples.VerifyExcelStream.verified.xlsx
+++ b/src/Tests/Samples.VerifyExcelStream.verified.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13996"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="DeterministicId4"/>
   </sheets>
   <calcPr fullPrecision="1" calcId="191029"/>
 </workbook>

--- a/src/Tests/Samples.VerifyExcelStream.verified.xlsx
+++ b/src/Tests/Samples.VerifyExcelStream.verified.xlsx
@@ -4,17 +4,18 @@
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13996"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13996" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="DeterministicId4"/>
+    <sheet name="Evaluation Warning" sheetId="2" r:id="DeterministicId5"/>
   </sheets>
   <calcPr fullPrecision="1" calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="30" count="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="33" count="190">
   <si>
     <t>First Name</t>
   </si>
@@ -104,13 +105,86 @@
   </si>
   <si>
     <t>Formula</t>
+  </si>
+  <si>
+    <t>https://www.syncfusion.com/account/claim-license-key?pl=ZXhjZWwsc3ByZWFkc2hlZXRlZGl0b3IsZ3JpZHNkaw==&amp;vs=MzQuMS4yOQ==</t>
+  </si>
+  <si>
+    <r>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="0"/>
+      </rPr>
+      <t>Created with a trial version of Syncfusion Excel library or registered the wrong key in your application. Click</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF0563C1"/>
+        <rFont val="Calibri"/>
+        <charset val="0"/>
+      </rPr>
+      <t xml:space="preserve"> here</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="0"/>
+      </rPr>
+      <t xml:space="preserve"> to obtain the valid key.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Tahoma"/>
+        <charset val="0"/>
+      </rPr>
+      <t>Created with a trial version of Syncfusion Excel library or registered the wrong key in your application. Click</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FF0563C1"/>
+        <rFont val="Tahoma"/>
+        <charset val="0"/>
+      </rPr>
+      <t xml:space="preserve"> here</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Tahoma"/>
+        <charset val="0"/>
+      </rPr>
+      <t xml:space="preserve"> to obtain the valid key.</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <fonts count="3">
+  <fonts count="11">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -128,6 +202,60 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF0563C1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <u val="single"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <u val="single"/>
+      <sz val="10"/>
+      <color rgb="000563C1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="000563C1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Tahoma"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF0563C1"/>
+      <name val="Tahoma"/>
       <charset val="0"/>
     </font>
   </fonts>
@@ -154,16 +282,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -176,6 +308,96 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>323422</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="0" name="TextBox 2">
+          <a:hlinkClick xmlns:p7="http://schemas.openxmlformats.org/officeDocument/2006/relationships" p7:id="rId1" tooltip="https://www.syncfusion.com/account/claim-license-key?pl=ZXhjZWwsc3ByZWFkc2hlZXRlZGl0b3IsZ3JpZHNkaw==&amp;vs=MzQuMS4yOQ=="/>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="18900000">
+          <a:off x="0" y="1"/>
+          <a:ext cx="2076450" cy="1557338"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF">
+            <a:alpha val="10000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-AU" b="1" i="0" sz="1200">
+              <a:solidFill>
+                <a:srgbClr val="FF0000">
+                  <a:alpha val="30000"/>
+                </a:srgbClr>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:rPr>
+            <a:t>Created with a trial version of Syncfusion Excel library or registered the 
+wrong key in your application. Click</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-AU" b="1" i="0" sz="1200">
+              <a:solidFill>
+                <a:srgbClr val="0563C1">
+                  <a:alpha val="30000"/>
+                </a:srgbClr>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:rPr>
+            <a:t> here</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-AU" b="1" i="0" sz="1200">
+              <a:solidFill>
+                <a:srgbClr val="FF0000">
+                  <a:alpha val="30000"/>
+                </a:srgbClr>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:rPr>
+            <a:t> to obtain the valid key.</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-AU" b="1" i="0" sz="1200">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:latin typeface="Calibri"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -476,7 +698,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
-  <dimension ref="A1:X1000"/>
+  <dimension ref="A1:X1001"/>
   <sheetFormatPr defaultColWidth="14.46484375" customHeight="true" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="7" width="11.5703125" customWidth="1"/>
@@ -548,7 +770,7 @@
         <v>1562</v>
       </c>
       <c r="H2">
-        <f>G2+A2</f>
+        <f ca="1">G2+A2</f>
         <v>1563</v>
       </c>
     </row>
@@ -575,7 +797,7 @@
         <v>1582</v>
       </c>
       <c r="H3">
-        <f>G3+A3</f>
+        <f ca="1">G3+A3</f>
         <v>1584</v>
       </c>
     </row>
@@ -602,7 +824,7 @@
         <v>2587</v>
       </c>
       <c r="H4">
-        <f>G4+A4</f>
+        <f ca="1">G4+A4</f>
         <v>2590</v>
       </c>
     </row>
@@ -629,7 +851,7 @@
         <v>3549</v>
       </c>
       <c r="H5">
-        <f>G5+A5</f>
+        <f ca="1">G5+A5</f>
         <v>3553</v>
       </c>
     </row>
@@ -656,7 +878,7 @@
         <v>2468</v>
       </c>
       <c r="H6">
-        <f>G6+A6</f>
+        <f ca="1">G6+A6</f>
         <v>2473</v>
       </c>
     </row>
@@ -683,7 +905,7 @@
         <v>2554</v>
       </c>
       <c r="H7">
-        <f>G7+A7</f>
+        <f ca="1">G7+A7</f>
         <v>2560</v>
       </c>
     </row>
@@ -710,7 +932,7 @@
         <v>3598</v>
       </c>
       <c r="H8">
-        <f>G8+A8</f>
+        <f ca="1">G8+A8</f>
         <v>3605</v>
       </c>
     </row>
@@ -737,7 +959,7 @@
         <v>2456</v>
       </c>
       <c r="H9">
-        <f>G9+A9</f>
+        <f ca="1">G9+A9</f>
         <v>2464</v>
       </c>
     </row>
@@ -764,7 +986,7 @@
         <v>6548</v>
       </c>
       <c r="H10">
-        <f>G10+A10</f>
+        <f ca="1">G10+A10</f>
         <v>6557</v>
       </c>
     </row>
@@ -791,7 +1013,7 @@
         <v>1562</v>
       </c>
       <c r="H11">
-        <f>G11+A11</f>
+        <f ca="1">G11+A11</f>
         <v>1563</v>
       </c>
     </row>
@@ -818,7 +1040,7 @@
         <v>1582</v>
       </c>
       <c r="H12">
-        <f>G12+A12</f>
+        <f ca="1">G12+A12</f>
         <v>1584</v>
       </c>
     </row>
@@ -845,7 +1067,7 @@
         <v>2587</v>
       </c>
       <c r="H13">
-        <f>G13+A13</f>
+        <f ca="1">G13+A13</f>
         <v>2590</v>
       </c>
     </row>
@@ -872,7 +1094,7 @@
         <v>3549</v>
       </c>
       <c r="H14">
-        <f>G14+A14</f>
+        <f ca="1">G14+A14</f>
         <v>3553</v>
       </c>
     </row>
@@ -899,7 +1121,7 @@
         <v>2468</v>
       </c>
       <c r="H15">
-        <f>G15+A15</f>
+        <f ca="1">G15+A15</f>
         <v>2473</v>
       </c>
     </row>
@@ -926,7 +1148,7 @@
         <v>2554</v>
       </c>
       <c r="H16">
-        <f>G16+A16</f>
+        <f ca="1">G16+A16</f>
         <v>2560</v>
       </c>
     </row>
@@ -953,7 +1175,7 @@
         <v>3598</v>
       </c>
       <c r="H17">
-        <f>G17+A17</f>
+        <f ca="1">G17+A17</f>
         <v>3605</v>
       </c>
     </row>
@@ -980,7 +1202,7 @@
         <v>2456</v>
       </c>
       <c r="H18">
-        <f>G18+A18</f>
+        <f ca="1">G18+A18</f>
         <v>2464</v>
       </c>
     </row>
@@ -1007,7 +1229,7 @@
         <v>6548</v>
       </c>
       <c r="H19">
-        <f>G19+A19</f>
+        <f ca="1">G19+A19</f>
         <v>6557</v>
       </c>
     </row>
@@ -1034,7 +1256,7 @@
         <v>1562</v>
       </c>
       <c r="H20">
-        <f>G20+A20</f>
+        <f ca="1">G20+A20</f>
         <v>1563</v>
       </c>
     </row>
@@ -1061,7 +1283,7 @@
         <v>1582</v>
       </c>
       <c r="H21">
-        <f>G21+A21</f>
+        <f ca="1">G21+A21</f>
         <v>1584</v>
       </c>
     </row>
@@ -1088,7 +1310,7 @@
         <v>2587</v>
       </c>
       <c r="H22">
-        <f>G22+A22</f>
+        <f ca="1">G22+A22</f>
         <v>2590</v>
       </c>
     </row>
@@ -1115,7 +1337,7 @@
         <v>3549</v>
       </c>
       <c r="H23">
-        <f>G23+A23</f>
+        <f ca="1">G23+A23</f>
         <v>3553</v>
       </c>
     </row>
@@ -1142,7 +1364,7 @@
         <v>2468</v>
       </c>
       <c r="H24">
-        <f>G24+A24</f>
+        <f ca="1">G24+A24</f>
         <v>2473</v>
       </c>
     </row>
@@ -1169,7 +1391,7 @@
         <v>2554</v>
       </c>
       <c r="H25">
-        <f>G25+A25</f>
+        <f ca="1">G25+A25</f>
         <v>2560</v>
       </c>
     </row>
@@ -1196,7 +1418,7 @@
         <v>3598</v>
       </c>
       <c r="H26">
-        <f>G26+A26</f>
+        <f ca="1">G26+A26</f>
         <v>3605</v>
       </c>
     </row>
@@ -1223,7 +1445,7 @@
         <v>2456</v>
       </c>
       <c r="H27">
-        <f>G27+A27</f>
+        <f ca="1">G27+A27</f>
         <v>2464</v>
       </c>
     </row>
@@ -1250,7 +1472,7 @@
         <v>6548</v>
       </c>
       <c r="H28">
-        <f>G28+A28</f>
+        <f ca="1">G28+A28</f>
         <v>6557</v>
       </c>
     </row>
@@ -1277,7 +1499,7 @@
         <v>1562</v>
       </c>
       <c r="H29">
-        <f>G29+A29</f>
+        <f ca="1">G29+A29</f>
         <v>1563</v>
       </c>
     </row>
@@ -1304,7 +1526,7 @@
         <v>1582</v>
       </c>
       <c r="H30">
-        <f>G30+A30</f>
+        <f ca="1">G30+A30</f>
         <v>1584</v>
       </c>
     </row>
@@ -1331,7 +1553,7 @@
         <v>2587</v>
       </c>
       <c r="H31">
-        <f>G31+A31</f>
+        <f ca="1">G31+A31</f>
         <v>2590</v>
       </c>
     </row>
@@ -1358,7 +1580,7 @@
         <v>3549</v>
       </c>
       <c r="H32">
-        <f>G32+A32</f>
+        <f ca="1">G32+A32</f>
         <v>3553</v>
       </c>
     </row>
@@ -1385,7 +1607,7 @@
         <v>2468</v>
       </c>
       <c r="H33">
-        <f>G33+A33</f>
+        <f ca="1">G33+A33</f>
         <v>2473</v>
       </c>
     </row>
@@ -1412,7 +1634,7 @@
         <v>2554</v>
       </c>
       <c r="H34">
-        <f>G34+A34</f>
+        <f ca="1">G34+A34</f>
         <v>2560</v>
       </c>
     </row>
@@ -1439,7 +1661,7 @@
         <v>3598</v>
       </c>
       <c r="H35">
-        <f>G35+A35</f>
+        <f ca="1">G35+A35</f>
         <v>3605</v>
       </c>
     </row>
@@ -1466,7 +1688,7 @@
         <v>2456</v>
       </c>
       <c r="H36">
-        <f>G36+A36</f>
+        <f ca="1">G36+A36</f>
         <v>2464</v>
       </c>
     </row>
@@ -1493,7 +1715,7 @@
         <v>6548</v>
       </c>
       <c r="H37">
-        <f>G37+A37</f>
+        <f ca="1">G37+A37</f>
         <v>6557</v>
       </c>
     </row>
@@ -1520,7 +1742,7 @@
         <v>1562</v>
       </c>
       <c r="H38">
-        <f>G38+A38</f>
+        <f ca="1">G38+A38</f>
         <v>1563</v>
       </c>
     </row>
@@ -1547,7 +1769,7 @@
         <v>1582</v>
       </c>
       <c r="H39">
-        <f>G39+A39</f>
+        <f ca="1">G39+A39</f>
         <v>1584</v>
       </c>
     </row>
@@ -1574,7 +1796,7 @@
         <v>2587</v>
       </c>
       <c r="H40">
-        <f>G40+A40</f>
+        <f ca="1">G40+A40</f>
         <v>2590</v>
       </c>
     </row>
@@ -1601,7 +1823,7 @@
         <v>3549</v>
       </c>
       <c r="H41">
-        <f>G41+A41</f>
+        <f ca="1">G41+A41</f>
         <v>3553</v>
       </c>
     </row>
@@ -1628,7 +1850,7 @@
         <v>2468</v>
       </c>
       <c r="H42">
-        <f>G42+A42</f>
+        <f ca="1">G42+A42</f>
         <v>2473</v>
       </c>
     </row>
@@ -1655,7 +1877,7 @@
         <v>2554</v>
       </c>
       <c r="H43">
-        <f>G43+A43</f>
+        <f ca="1">G43+A43</f>
         <v>2560</v>
       </c>
     </row>
@@ -1682,7 +1904,7 @@
         <v>3598</v>
       </c>
       <c r="H44">
-        <f>G44+A44</f>
+        <f ca="1">G44+A44</f>
         <v>3605</v>
       </c>
     </row>
@@ -1709,7 +1931,7 @@
         <v>2456</v>
       </c>
       <c r="H45">
-        <f>G45+A45</f>
+        <f ca="1">G45+A45</f>
         <v>2464</v>
       </c>
     </row>
@@ -1736,7 +1958,7 @@
         <v>6548</v>
       </c>
       <c r="H46">
-        <f>G46+A46</f>
+        <f ca="1">G46+A46</f>
         <v>6557</v>
       </c>
     </row>
@@ -2694,13 +2916,52 @@
     <row r="998" ht="12.75" customHeight="1"/>
     <row r="999" ht="12.75" customHeight="1"/>
     <row r="1000" ht="12.75" customHeight="1"/>
+    <row r="1001" spans="1:1" ht="12.75">
+      <c r="A1001" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1001:T1001"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A1001" r:id="DeterministicId2" tooltip="https://www.syncfusion.com/account/claim-license-key?pl=ZXhjZWwsc3ByZWFkc2hlZXRlZGl0b3IsZ3JpZHNkaw==&amp;vs=MzQuMS4yOQ==" display="Created with a trial version of Syncfusion Excel library or registered the wrong key in your application. Click here to obtain the valid key."/>
+  </hyperlinks>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter scaleWithDoc="1" alignWithMargins="1" differentFirst="0" differentOddEven="0">
     <oddHeader>&amp;C&amp;A</oddHeader>
     <oddFooter>&amp;CPage &amp;P</oddFooter>
   </headerFooter>
+  <drawing r:id="DeterministicId1"/>
+  <extLst/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FFFF4500"/>
+  </sheetPr>
+  <dimension ref="A10"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetData>
+    <row r="10" spans="1:1" ht="25" customHeight="1">
+      <c r="A10" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="RNBtkiF2xgKLR9Fj9h2jNVW2/MGC660A7/JlbqQVI4Gbp2BOT6NF5rzUxmAlyJYoX9gLuXactHBdWsOfcaW9gA==" saltValue="3sPROVb7bsq+nuIS4YIikw==" spinCount="500" sheet="1" objects="1" scenarios="1" pivotTables="1"/>
+  <mergeCells count="1">
+    <mergeCell ref="A10:S10"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A10" r:id="DeterministicId1" tooltip="https://www.syncfusion.com/account/claim-license-key?pl=ZXhjZWwsc3ByZWFkc2hlZXRlZGl0b3IsZ3JpZHNkaw==&amp;vs=MzQuMS4yOQ==" display="Created with a trial version of Syncfusion Excel library or registered the wrong key in your application. Click here to obtain the valid key."/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter scaleWithDoc="1" alignWithMargins="0" differentFirst="0" differentOddEven="0"/>
   <extLst/>
 </worksheet>
 </file>
--- a/src/Tests/Samples.VerifyExcelStream.verified.xlsx
+++ b/src/Tests/Samples.VerifyExcelStream.verified.xlsx
@@ -2953,7 +2953,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="RNBtkiF2xgKLR9Fj9h2jNVW2/MGC660A7/JlbqQVI4Gbp2BOT6NF5rzUxmAlyJYoX9gLuXactHBdWsOfcaW9gA==" saltValue="3sPROVb7bsq+nuIS4YIikw==" spinCount="500" sheet="1" objects="1" scenarios="1" pivotTables="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="CEM2+DGKILHNjKufmNgZXGhxIvDTC4W0skPLvhDfoEhDxuRoqDeipHFBek45kUO5I5MSOA7wz1Ksip5SniSVUw==" saltValue="edha6h/+/SqxsIai84Jh4A==" spinCount="500" sheet="1" objects="1" scenarios="1" pivotTables="1"/>
   <mergeCells count="1">
     <mergeCell ref="A10:S10"/>
   </mergeCells>

--- a/src/Tests/Samples.VerifyExcelStream.verified.xlsx
+++ b/src/Tests/Samples.VerifyExcelStream.verified.xlsx
@@ -2953,7 +2953,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="CEM2+DGKILHNjKufmNgZXGhxIvDTC4W0skPLvhDfoEhDxuRoqDeipHFBek45kUO5I5MSOA7wz1Ksip5SniSVUw==" saltValue="edha6h/+/SqxsIai84Jh4A==" spinCount="500" sheet="1" objects="1" scenarios="1" pivotTables="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="DeterministicHash" saltValue="DeterministicSalt" spinCount="500" sheet="1" objects="1" scenarios="1" pivotTables="1"/>
   <mergeCells count="1">
     <mergeCell ref="A10:S10"/>
   </mergeCells>
